--- a/Concast_CRMGUIFramework/Testdata/testscriptdata.xlsx
+++ b/Concast_CRMGUIFramework/Testdata/testscriptdata.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="51">
   <si>
     <t>TC-ID</t>
   </si>
@@ -92,28 +92,31 @@
     <t>createOrgTest</t>
   </si>
   <si>
+    <t>facebook_12</t>
+  </si>
+  <si>
+    <t>pass</t>
+  </si>
+  <si>
+    <t>Organization Name</t>
+  </si>
+  <si>
+    <t>industries</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>oppertunity</t>
+  </si>
+  <si>
+    <t>tc-02</t>
+  </si>
+  <si>
+    <t>createorgwithType</t>
+  </si>
+  <si>
     <t>facebook_</t>
-  </si>
-  <si>
-    <t>pass</t>
-  </si>
-  <si>
-    <t>Organization Name</t>
-  </si>
-  <si>
-    <t>industries</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>oppertunity</t>
-  </si>
-  <si>
-    <t>tc-02</t>
-  </si>
-  <si>
-    <t>createorgwithType</t>
   </si>
   <si>
     <t>Energy</t>
@@ -1541,16 +1544,16 @@
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1564,7 +1567,7 @@
         <v>22</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E7" s="1"/>
     </row>
@@ -1573,10 +1576,10 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>17</v>
@@ -1599,10 +1602,10 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1624,13 +1627,13 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
@@ -1638,24 +1641,24 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
         <v>3</v>
@@ -1666,21 +1669,21 @@
         <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
         <v>3</v>
@@ -1691,10 +1694,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1715,15 +1718,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
